--- a/mlef_pipeline/results/DCR/HIGH_PDL1/RWD_DP_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/HIGH_PDL1/RWD_DP_PYRAD/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.54 ± 0.12</t>
+          <t>0.65 ± 0.11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.34 ± 0.10</t>
+          <t>0.44 ± 0.07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.70 ± 0.39</t>
+          <t>0.74 ± 0.27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.25 ± 0.38</t>
+          <t>0.33 ± 0.38</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.14 ± 0.27</t>
+          <t>0.23 ± 0.41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.64 ± 0.26</t>
+          <t>0.65 ± 0.26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F4" t="n">
